--- a/data/trans_dic/IP09-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP09-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen actualmente esa dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Menores que padecen actualmente esa dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,32 +717,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,67; 58,75</t>
+          <t>7,48; 58,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,8; 64,97</t>
+          <t>20,72; 64,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,81</t>
+          <t>0,0; 75,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 96,21</t>
+          <t>0,0; 97,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,16; 60,17</t>
+          <t>13,25; 59,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,3; 81,3</t>
+          <t>32,86; 84,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,22; 76,26</t>
+          <t>23,4; 76,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,18; 49,07</t>
+          <t>14,13; 51,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,64; 68,14</t>
+          <t>35,61; 67,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,24; 70,34</t>
+          <t>11,68; 72,02</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,6; 86,24</t>
+          <t>33,44; 84,49</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,18; 40,1</t>
+          <t>16,12; 41,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,06; 45,45</t>
+          <t>24,69; 45,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,81; 57,19</t>
+          <t>28,52; 57,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,18; 46,92</t>
+          <t>20,88; 47,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,89; 39,99</t>
+          <t>21,09; 42,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,75; 41,66</t>
+          <t>23,38; 42,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,51; 56,71</t>
+          <t>30,22; 56,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,61; 40,77</t>
+          <t>15,45; 40,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,37; 36,99</t>
+          <t>21,12; 36,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,17; 39,96</t>
+          <t>26,99; 40,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,75; 52,21</t>
+          <t>33,6; 53,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,18; 39,12</t>
+          <t>19,45; 38,14</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 34,39</t>
+          <t>3,7; 37,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,24; 50,07</t>
+          <t>12,12; 48,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,42; 62,19</t>
+          <t>17,77; 62,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,57; 53,73</t>
+          <t>14,58; 49,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,98; 40,13</t>
+          <t>9,76; 40,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,34; 42,35</t>
+          <t>7,4; 39,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,02; 75,01</t>
+          <t>27,73; 80,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,06; 44,37</t>
+          <t>10,64; 47,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,27; 31,37</t>
+          <t>10,3; 32,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,9; 36,2</t>
+          <t>14,05; 36,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29,13; 64,2</t>
+          <t>28,39; 62,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,53; 42,15</t>
+          <t>16,19; 42,59</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,34; 32,43</t>
+          <t>15,2; 33,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,05; 42,84</t>
+          <t>26,84; 43,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,68; 52,38</t>
+          <t>29,11; 51,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,7; 56,99</t>
+          <t>27,69; 58,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,67; 36,82</t>
+          <t>21,42; 37,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,05; 42,65</t>
+          <t>26,02; 41,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,37; 58,14</t>
+          <t>34,37; 56,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,61; 39,25</t>
+          <t>19,14; 39,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,95; 33,06</t>
+          <t>20,57; 32,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,93; 40,34</t>
+          <t>28,31; 40,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,85; 52,0</t>
+          <t>34,9; 50,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,71; 42,58</t>
+          <t>25,88; 43,54</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen actualmente esa dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5355</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6740</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3431</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6946</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1479</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>5428</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5346</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2878</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>12169</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>585; 4601</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2641; 8271</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3362</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 9115</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1373; 6215</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3796; 9768</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2773</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2553; 8393</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2570; 9437</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>8652; 16508</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>843; 5201</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>6784; 17143</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>8013</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18961</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13259</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12029</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>16061</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>22883</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>16745</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>18432</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>24073</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>41844</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>30004</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>30461</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4926; 12771</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>13550; 25180</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>8865; 17727</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>7686; 17514</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>11273; 22514</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>16462; 29583</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>11639; 21692</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>10171; 26770</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>17744; 30892</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>33810; 50363</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>23385; 37187</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>19962; 39141</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2873</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4081</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4418</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5132</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4550</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4422</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5552</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5740</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>7423</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>8503</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9970</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>10872</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>661; 6648</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1847; 7316</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2061; 7219</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2419; 8246</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1920; 7929</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1516; 8025</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2817; 8192</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2372; 10524</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3866; 12337</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>5019; 13197</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6177; 13625</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>6297; 16565</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>12800</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>28397</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19077</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23901</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>24042</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>34252</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>23775</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>29601</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>36842</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>62649</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>42852</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>53502</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>8551; 18823</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>22240; 35877</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>13716; 24245</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>17385; 37000</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>17885; 31518</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>26651; 42342</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>17685; 29248</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>18953; 38918</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>28746; 45033</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>52464; 74221</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>34396; 50248</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>41883; 70448</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP09-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP09-Estudios-trans_dic.xlsx
@@ -717,32 +717,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,48; 58,85</t>
+          <t>7,61; 54,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,72; 64,89</t>
+          <t>20,73; 65,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,57</t>
+          <t>0,0; 73,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 97,15</t>
+          <t>18,33; 96,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,25; 59,95</t>
+          <t>13,1; 59,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,86; 84,57</t>
+          <t>32,43; 81,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,4; 76,94</t>
+          <t>24,5; 75,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,13; 51,89</t>
+          <t>13,99; 48,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,61; 67,94</t>
+          <t>33,82; 67,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,68; 72,02</t>
+          <t>9,69; 68,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,44; 84,49</t>
+          <t>32,63; 85,21</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,12; 41,79</t>
+          <t>14,71; 40,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,69; 45,88</t>
+          <t>24,46; 45,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,52; 57,04</t>
+          <t>28,88; 57,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,88; 47,58</t>
+          <t>20,49; 45,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,09; 42,13</t>
+          <t>21,09; 40,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,38; 42,02</t>
+          <t>24,26; 43,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,22; 56,32</t>
+          <t>30,7; 56,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,45; 40,67</t>
+          <t>15,46; 40,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,12; 36,78</t>
+          <t>21,37; 36,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,99; 40,2</t>
+          <t>26,87; 40,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33,6; 53,44</t>
+          <t>32,62; 51,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,45; 38,14</t>
+          <t>20,03; 39,67</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 37,21</t>
+          <t>3,62; 35,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,12; 48,01</t>
+          <t>12,79; 48,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,77; 62,25</t>
+          <t>17,33; 63,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,58; 49,69</t>
+          <t>14,49; 52,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,76; 40,31</t>
+          <t>9,86; 40,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 39,2</t>
+          <t>9,55; 40,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,73; 80,64</t>
+          <t>28,42; 80,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,64; 47,19</t>
+          <t>11,38; 47,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,3; 32,87</t>
+          <t>10,98; 31,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,05; 36,95</t>
+          <t>13,83; 36,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,39; 62,63</t>
+          <t>29,45; 63,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,19; 42,59</t>
+          <t>16,9; 42,07</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,2; 33,47</t>
+          <t>14,64; 33,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,84; 43,29</t>
+          <t>26,58; 43,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,11; 51,45</t>
+          <t>29,7; 52,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,69; 58,93</t>
+          <t>27,16; 56,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,42; 37,76</t>
+          <t>21,85; 38,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,02; 41,34</t>
+          <t>26,19; 41,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,37; 56,85</t>
+          <t>35,03; 57,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,14; 39,3</t>
+          <t>20,14; 40,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,57; 32,23</t>
+          <t>20,38; 33,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,31; 40,06</t>
+          <t>28,71; 40,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34,9; 50,98</t>
+          <t>35,99; 52,31</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,88; 43,54</t>
+          <t>24,71; 42,72</t>
         </is>
       </c>
     </row>
@@ -1504,32 +1504,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>585; 4601</t>
+          <t>595; 4244</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2641; 8271</t>
+          <t>2643; 8383</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3362</t>
+          <t>0; 3285</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 9115</t>
+          <t>1720; 9069</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1373; 6215</t>
+          <t>1358; 6205</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3796; 9768</t>
+          <t>3746; 9401</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1539,27 +1539,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2553; 8393</t>
+          <t>2672; 8259</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2570; 9437</t>
+          <t>2543; 8770</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8652; 16508</t>
+          <t>8217; 16446</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>843; 5201</t>
+          <t>700; 4925</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6784; 17143</t>
+          <t>6621; 17289</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4926; 12771</t>
+          <t>4496; 12456</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13550; 25180</t>
+          <t>13424; 24869</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8865; 17727</t>
+          <t>8976; 17717</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7686; 17514</t>
+          <t>7541; 16780</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11273; 22514</t>
+          <t>11273; 21835</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16462; 29583</t>
+          <t>17080; 30285</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11639; 21692</t>
+          <t>11823; 21933</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10171; 26770</t>
+          <t>10172; 26971</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17744; 30892</t>
+          <t>17953; 30851</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33810; 50363</t>
+          <t>33663; 50625</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23385; 37187</t>
+          <t>22704; 36032</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19962; 39141</t>
+          <t>20557; 40707</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>661; 6648</t>
+          <t>646; 6422</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1847; 7316</t>
+          <t>1948; 7338</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2061; 7219</t>
+          <t>2010; 7393</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2419; 8246</t>
+          <t>2405; 8713</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1920; 7929</t>
+          <t>1940; 7963</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1516; 8025</t>
+          <t>1954; 8376</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2817; 8192</t>
+          <t>2887; 8193</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2372; 10524</t>
+          <t>2539; 10631</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3866; 12337</t>
+          <t>4120; 11885</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5019; 13197</t>
+          <t>4941; 13029</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6177; 13625</t>
+          <t>6408; 13768</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6297; 16565</t>
+          <t>6574; 16362</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8551; 18823</t>
+          <t>8235; 18927</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22240; 35877</t>
+          <t>22023; 35934</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13716; 24245</t>
+          <t>13995; 24775</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17385; 37000</t>
+          <t>17052; 35165</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17885; 31518</t>
+          <t>18238; 31815</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26651; 42342</t>
+          <t>26828; 42523</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17685; 29248</t>
+          <t>18024; 29737</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18953; 38918</t>
+          <t>19946; 39888</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28746; 45033</t>
+          <t>28478; 46224</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52464; 74221</t>
+          <t>53194; 74540</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>34396; 50248</t>
+          <t>35470; 51558</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>41883; 70448</t>
+          <t>39976; 69126</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP09-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP09-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33,09%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>60,14%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>53,32%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>53,6%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>24,49%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>42,01%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>31,47%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>71,84%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>33,09%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>60,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>53,32%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>48,56%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,61; 54,29</t>
+          <t>13,16; 60,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,73; 65,77</t>
+          <t>31,3; 81,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,84</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,33; 96,66</t>
+          <t>26,54; 79,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,1; 59,85</t>
+          <t>7,67; 58,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,43; 81,38</t>
+          <t>20,8; 64,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 74,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,5; 75,71</t>
+          <t>0,0; 78,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,99; 48,23</t>
+          <t>14,18; 49,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33,82; 67,69</t>
+          <t>32,64; 68,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,69; 68,19</t>
+          <t>11,24; 70,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,63; 85,21</t>
+          <t>27,18; 71,35</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30,05%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>32,51%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>43,48%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28,92%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>26,22%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>34,55%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>42,66%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>32,68%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>30,05%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>32,51%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>43,48%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,66%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,71; 40,76</t>
+          <t>19,89; 39,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,46; 45,31</t>
+          <t>23,75; 41,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,88; 57,01</t>
+          <t>30,51; 56,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,49; 45,59</t>
+          <t>16,99; 42,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,09; 40,86</t>
+          <t>14,18; 40,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,26; 43,02</t>
+          <t>25,06; 45,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,7; 56,95</t>
+          <t>28,81; 57,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,46; 40,98</t>
+          <t>21,38; 47,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,37; 36,73</t>
+          <t>21,37; 36,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,87; 40,41</t>
+          <t>26,17; 39,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,62; 51,78</t>
+          <t>32,75; 52,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,03; 39,67</t>
+          <t>20,36; 40,04</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>23,13%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21,6%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>54,65%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>26,88%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>16,08%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>26,78%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>38,1%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>30,93%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>23,13%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>21,6%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>54,65%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 35,95</t>
+          <t>9,98; 40,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,79; 48,15</t>
+          <t>10,34; 42,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,33; 63,75</t>
+          <t>28,02; 75,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,49; 52,51</t>
+          <t>11,31; 45,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,86; 40,48</t>
+          <t>3,55; 34,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,55; 40,91</t>
+          <t>12,24; 50,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,42; 80,65</t>
+          <t>16,42; 62,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,38; 47,67</t>
+          <t>14,29; 52,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,98; 31,66</t>
+          <t>10,27; 31,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,83; 36,48</t>
+          <t>13,9; 36,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29,45; 63,28</t>
+          <t>29,13; 64,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,9; 42,07</t>
+          <t>17,92; 42,58</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28,8%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>33,44%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>46,21%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>31,15%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>22,76%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>34,27%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>40,48%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>38,07%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>33,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>46,21%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,64; 33,65</t>
+          <t>21,67; 36,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,58; 43,36</t>
+          <t>26,05; 42,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,7; 52,57</t>
+          <t>35,37; 58,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,16; 56,01</t>
+          <t>19,96; 40,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,85; 38,11</t>
+          <t>14,34; 32,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,19; 41,52</t>
+          <t>26,05; 42,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,03; 57,8</t>
+          <t>29,68; 52,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,14; 40,28</t>
+          <t>22,96; 42,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,38; 33,08</t>
+          <t>20,95; 33,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,71; 40,23</t>
+          <t>28,93; 40,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,99; 52,31</t>
+          <t>35,85; 52,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,71; 42,72</t>
+          <t>24,58; 39,54</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3431</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6946</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1479</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5179</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1915</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>5355</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1400</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6740</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3431</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6946</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1479</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12169</t>
+          <t>6822</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>595; 4244</t>
+          <t>1364; 6238</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2643; 8383</t>
+          <t>3616; 9391</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3285</t>
+          <t>0; 2773</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1720; 9069</t>
+          <t>2565; 7668</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1358; 6205</t>
+          <t>600; 4593</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3746; 9401</t>
+          <t>2651; 8281</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2773</t>
+          <t>0; 3328</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2672; 8259</t>
+          <t>0; 3436</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2543; 8770</t>
+          <t>2578; 8924</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8217; 16446</t>
+          <t>7932; 16557</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>700; 4925</t>
+          <t>812; 5080</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6621; 17289</t>
+          <t>3818; 10023</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16061</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>22883</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16745</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17186</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>8013</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>18961</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>13259</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12029</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>16061</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>22883</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16745</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30461</t>
+          <t>29461</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4496; 12456</t>
+          <t>10629; 21372</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13424; 24869</t>
+          <t>16717; 29328</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8976; 17717</t>
+          <t>11753; 21841</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7541; 16780</t>
+          <t>10098; 25019</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11273; 21835</t>
+          <t>4333; 12256</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17080; 30285</t>
+          <t>13752; 24944</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11823; 21933</t>
+          <t>8955; 17772</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10172; 26971</t>
+          <t>7841; 17491</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17953; 30851</t>
+          <t>17950; 31069</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33663; 50625</t>
+          <t>32788; 50058</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22704; 36032</t>
+          <t>22790; 36336</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20557; 40707</t>
+          <t>19561; 38474</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4550</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4422</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5552</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5316</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>2873</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>4081</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>4418</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5132</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4550</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4422</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5552</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10872</t>
+          <t>10509</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>646; 6422</t>
+          <t>1964; 7894</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1948; 7338</t>
+          <t>2116; 8671</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2010; 7393</t>
+          <t>2847; 7621</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2405; 8713</t>
+          <t>2237; 9089</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1940; 7963</t>
+          <t>633; 6143</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1954; 8376</t>
+          <t>1866; 7631</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2887; 8193</t>
+          <t>1905; 7212</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2539; 10631</t>
+          <t>2459; 9040</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4120; 11885</t>
+          <t>3854; 11774</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4941; 13029</t>
+          <t>4963; 12929</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6408; 13768</t>
+          <t>6337; 13967</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6574; 16362</t>
+          <t>6629; 15752</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>24042</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>34252</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>23775</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>27682</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>12800</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>28397</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>19077</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>23901</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>24042</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>34252</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>23775</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>29601</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>53502</t>
+          <t>46792</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8235; 18927</t>
+          <t>18092; 30739</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22023; 35934</t>
+          <t>26680; 43680</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13995; 24775</t>
+          <t>18195; 29911</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17052; 35165</t>
+          <t>17739; 36240</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18238; 31815</t>
+          <t>8067; 18237</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26828; 42523</t>
+          <t>21589; 35499</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18024; 29737</t>
+          <t>13988; 24681</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19946; 39888</t>
+          <t>13376; 24933</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28478; 46224</t>
+          <t>29266; 46196</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>53194; 74540</t>
+          <t>53598; 74753</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35470; 51558</t>
+          <t>35337; 51256</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>39976; 69126</t>
+          <t>36173; 58177</t>
         </is>
       </c>
     </row>
